--- a/config/stage_config.xlsx
+++ b/config/stage_config.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.83203125" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,11 @@
           <t>next(下一幕场景,可空)</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_anims_from(动画清单路径,优先)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -638,7 +643,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>res://scenes/v3/stage_honden.tscn</t>
+          <t>res://scenes/v3/stage_night3.tscn</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_25d/animation_manifest.json</t>
         </is>
       </c>
     </row>
@@ -710,6 +720,11 @@
           <t>res://scenes/v3/truth.tscn</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_25d/animation_manifest.json</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -779,6 +794,11 @@
           <t>res://scenes/v3/stage_corridor.tscn</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_25d/animation_manifest.json</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -854,6 +874,167 @@
       <c r="Q5" t="inlineStr">
         <is>
           <t>山道：平地 y990 → 1080 起石阶至右上平台（遮罩 assets/bg/walkmasks/mountain_path.png 已边缘吸附，可后台细涂）</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_25d/animation_manifest.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>回廊深处（第三夜·纸人抬棺）</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>第三夜探索：corridor_walk 深夜层，雾更重</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>res://assets/bg/corridor_walk.png</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_idle.png</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>240</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[{"name": "凛音", "art": "res://assets/chars/rinne_idle.png", "hp": 30, "hp_max": 30, "fear": 0, "fear_max": 100, "hand": 3}, {"name": "薄荷", "art": "res://assets/chars/hakuyo_idle.png", "hp": 26, "hp_max": 26, "fear": 0, "fear_max": 100, "hand": 4}]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[120, 1920]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[[0, 930], [600, 930], [1200, 900], [2048, 880]]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>{"idle": ["res://assets/chars/anims/rinne_idle_f1.png", "res://assets/chars/anims/rinne_idle_f2.png", "res://assets/chars/anims/rinne_idle_f3.png", "res://assets/chars/anims/rinne_idle_f4.png"], "walk": ["res://assets/chars/anims/rinne_walk_f1.png", "res://assets/chars/anims/rinne_walk_f2.png", "res://assets/chars/anims/rinne_walk_f3.png", "res://assets/chars/anims/rinne_walk_f4.png", "res://assets/chars/anims/rinne_walk_f5.png", "res://assets/chars/anims/rinne_walk_f6.png"], "fps": 8}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>res://scenes/v3/stage_night4.tscn</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_25d/animation_manifest.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>本殿黄昏（第四夜·棺中镜）</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>第四夜探索：honden_dusk 棺停御神木下</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>res://assets/bg/honden_dusk.png</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_idle.png</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>500</v>
+      </c>
+      <c r="J7" t="n">
+        <v>240</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>[{"name": "凛音", "art": "res://assets/chars/rinne_idle.png", "hp": 30, "hp_max": 30, "fear": 0, "fear_max": 100, "hand": 3}, {"name": "薄荷", "art": "res://assets/chars/hakuyo_idle.png", "hp": 26, "hp_max": 26, "fear": 0, "fear_max": 100, "hand": 4}]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[120, 1920]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[[0, 920], [700, 920], [1300, 890], [2048, 860]]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{"idle": ["res://assets/chars/anims/rinne_idle_f1.png", "res://assets/chars/anims/rinne_idle_f2.png", "res://assets/chars/anims/rinne_idle_f3.png", "res://assets/chars/anims/rinne_idle_f4.png"], "walk": ["res://assets/chars/anims/rinne_walk_f1.png", "res://assets/chars/anims/rinne_walk_f2.png", "res://assets/chars/anims/rinne_walk_f3.png", "res://assets/chars/anims/rinne_walk_f4.png", "res://assets/chars/anims/rinne_walk_f5.png", "res://assets/chars/anims/rinne_walk_f6.png"], "fps": 8}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>res://scenes/v3/stage_honden.tscn</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>res://assets/chars/rinne_25d/animation_manifest.json</t>
         </is>
       </c>
     </row>
@@ -868,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.83203125" customWidth="1" min="1" max="1"/>
@@ -1209,6 +1390,134 @@
       <c r="O5" t="inlineStr">
         <is>
           <t>仪式入口线索（GDD §8.3）：调查残文 → 转场回廊守灯仪式。坐标为世界坐标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>night3_procession</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>coffin_procession</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>抬棺队列</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H6" t="n">
+        <v>575</v>
+      </c>
+      <c r="I6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"kind": "cold_light", "color": "hi_500", "flicker_speed": 3.2, "glow_radius": 110, "shape": "none"}</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>纸人形列队而过，抬着一口空棺。棺盖缝隙透出微光——有节奏地，亮三下。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>空棺轻得像一页纸，又沉得压弯了抬棺的纸肩。第三声叩响落下，队列齐刷刷转向了你。</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>res://scenes/v3/battle_night3.tscn</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>第三夜画面线索（第一章棺女）：夜行抬棺——棺中三叩，像在数谁的脚步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>night4_mirror</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mirror_in_coffin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>reflection</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>棺中之镜</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H7" t="n">
+        <v>575</v>
+      </c>
+      <c r="I7" t="n">
+        <v>150</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{"kind": "cold_light", "color": "hi_500", "flicker_speed": 3.2, "glow_radius": 110, "shape": "none"}</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>棺底嵌着一面铜镜。镜中没有你的倒影——只有一个穿嫁衣的背影。</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>镜面冰凉。她隔着七十年望过来，唇形像是在说：「送我走。」</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>res://scenes/v3/battle_night4.tscn</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>第四夜画面线索（第一章棺女）：棺中镜——照见棺女生前模样。</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1594,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>逢魔神社 · 夜巡（样章结案）</t>
+          <t>逢魔神社 · 夜巡（第一章「棺女」结案）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GDD §6 样章真相：灯笼/钟鸣/棺守三线归一；两种处理方式有余波差异</t>
+          <t>第一章五夜真相：棺女小夜——七十年前没送成的葬；双分支结局（送行/镇守），镇守线留第二章伏笔</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"t1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "三夜查明白了。参道水钵里的灯笼、回廊自鸣的吊钟、棺守等的人——都是同一件事：几十年前那场没送成的葬。", "next": "t2"}, "t2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "钟鸣不是警报，是送行钟。纸人形列队不是在作乱，是在等一个替他们把仪式办完的人。第三次叩门，是它最后的耐心。", "next": "t3"}, "t3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "现在，轮到我了。", "choices": [{"text": "（送行）念引路词，送它远行", "next": "e_send"}, {"text": "（镇守）立朱印，镇其归处", "next": "e_seal"}]}, "e_send": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "引灯走在前，铃声断在后。棺守的执念随着火光淡下去——回廊尽头，晨雾第一次照了进来。", "next": "t4"}, "e_seal": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "朱印落在棺头，钟声沉进地底。它不会再等了——有些送别，是以不再等待的方式完成的。", "next": "t4"}, "t4": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "案件已结。退魔寮的绘卷上，多了一页会自己发暖的残页。"}}</t>
+          <t>{"t1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "五夜查明白了。水钵里的灯笼、无风的钟、夜行的棺、棺中的镜——都是同一件事：七十年前，一场没送成的葬。", "next": "t2"}, "t2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "钟鸣不是警报，是送行钟。纸人形列队不是在作乱，是在等一个替他们把仪式办完的人。第三次叩门，是它最后的耐心。", "next": "t3"}, "t3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "现在，轮到我了。", "next": "", "choices": [{"text": "（送行）念引路词，送它远行", "next": "e_send"}, {"text": "（镇守）立朱印，镇其归处", "next": "e_seal"}]}, "e_send": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……谢谢你。七十年了，终于有人听懂钟声里的意思。", "next": "s1"}, "s1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（引路词）魂兮归来，莫恋此乡。灯前有路，路尽有光——去吧。", "next": "s2"}, "s2": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "再见了，祭主爷爷。这七十年的更次，辛苦你了。", "next": "s3"}, "s3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（她的身影随灯火轻轻一礼，淡下去。老祭主的纸躯委顿于地，像终于卸下了肩上的棺。逢魔之刻的雾，第一次在天亮前散尽了。）", "next": ""}, "e_seal": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（立朱印）以逢魔之名，镇其归处。自此异象不起，百夜无更。", "next": "z1"}, "z1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（朱印落下，钟鸣、纸响、棺纹一齐寂然。只有棺底极轻极轻地——叩了一声。像还有话，被封在了里面。）", "next": "z2"}, "z2": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……没关系。已经，习惯了。", "next": ""}}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/config/stage_config.xlsx
+++ b/config/stage_config.xlsx
@@ -1438,12 +1438,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>纸人形列队而过，抬着一口空棺。棺盖缝隙透出微光——有节奏地，亮三下。</t>
+          <t>纸人形列队而过，抬着一口空棺。棺盖缝隙透出微光——有节奏地，亮三下，熄三下。薄荷拉住你的袖子：「它们走了七十年的同一条路，一步都没有偏过。」</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>空棺轻得像一页纸，又沉得压弯了抬棺的纸肩。第三声叩响落下，队列齐刷刷转向了你。</t>
+          <t>空棺轻得像一页纸，又沉得压弯了抬棺的纸肩。第三声叩响落下，队列齐刷刷转向了你——你没有让路。它们也没有。这座神社在等一个先开口的人。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>第三夜画面线索（第一章棺女）：夜行抬棺——棺中三叩，像在数谁的脚步。</t>
+          <t>第三夜画面线索（第一章棺女）：夜行抬棺——棺中三叩，是催促，也是路标。</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>棺底嵌着一面铜镜。镜中没有你的倒影——只有一个穿嫁衣的背影。</t>
+          <t>棺底嵌着一面铜镜。镜中没有你的倒影——只有一个穿嫁衣的背影。薄荷听了一会儿，轻声说：「她问，山下顾家……是不是派人来接她了。」</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>镜面冰凉。她隔着七十年望过来，唇形像是在说：「送我走。」</t>
+          <t>镜面冰凉，映出的却不是死相——是七十年前婚礼前夜，那个还在等灯的姑娘。她的唇形很慢，像隔着很深的水：「送我走。」</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>第四夜画面线索（第一章棺女）：棺中镜——照见棺女生前模样。</t>
+          <t>第四夜画面线索（第一章棺女）：棺中镜——照见小夜生前模样，顾家旧约浮出水面。</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"t1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "五夜查明白了。水钵里的灯笼、无风的钟、夜行的棺、棺中的镜——都是同一件事：七十年前，一场没送成的葬。", "next": "t2"}, "t2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "钟鸣不是警报，是送行钟。纸人形列队不是在作乱，是在等一个替他们把仪式办完的人。第三次叩门，是它最后的耐心。", "next": "t3"}, "t3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "现在，轮到我了。", "next": "", "choices": [{"text": "（送行）念引路词，送它远行", "next": "e_send"}, {"text": "（镇守）立朱印，镇其归处", "next": "e_seal"}]}, "e_send": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……谢谢你。七十年了，终于有人听懂钟声里的意思。", "next": "s1"}, "s1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（引路词）魂兮归来，莫恋此乡。灯前有路，路尽有光——去吧。", "next": "s2"}, "s2": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "再见了，祭主爷爷。这七十年的更次，辛苦你了。", "next": "s3"}, "s3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（她的身影随灯火轻轻一礼，淡下去。老祭主的纸躯委顿于地，像终于卸下了肩上的棺。逢魔之刻的雾，第一次在天亮前散尽了。）", "next": ""}, "e_seal": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（立朱印）以逢魔之名，镇其归处。自此异象不起，百夜无更。", "next": "z1"}, "z1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（朱印落下，钟鸣、纸响、棺纹一齐寂然。只有棺底极轻极轻地——叩了一声。像还有话，被封在了里面。）", "next": "z2"}, "z2": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……没关系。已经，习惯了。", "next": ""}}</t>
+          <t>{"t1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "五夜查明白了。水钵里的灯笼、无风的钟、夜行的棺、棺中的镜——都是同一件事：七十年前，一场没送成的葬。", "next": "t2"}, "t2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "钟鸣不是警报，是送行钟。纸人形列队不是在作乱，是在等一个替他们把仪式办完的人。第三次叩门，是它最后的耐心。", "next": "t3"}, "t3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "现在，轮到我了。", "next": "", "choices": [{"text": "（送行）念引路词，送它远行", "next": "e_send"}, {"text": "（镇守）立朱印，镇其归处", "next": "e_seal"}]}, "e_send": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……谢谢你。七十年了，终于有人听懂钟声里的意思。", "next": "s1"}, "s1": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "我叫小夜。山下村子，顾家的媳妇——虽然还没来得及过门。（她低头看自己的手）外头……仗打完了吗？", "next": "s2"}, "s2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "打完了。七十年前就打完了。村子的人迁去了南边，开枝散叶，活得很好。顾家的后人里，有一个做了退魔师——她让我替她还一盏灯。", "next": "s3"}, "s3": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "那就好，那就好……（她转向棺守的纸躯，端端正正福了一礼）祭主爷爷，更次你替我数了三万次，辛苦你了。", "next": "s4"}, "s4": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（引路词）魂兮归来，莫恋此乡。灯前有路，路尽有光。顾氏小夜——拜堂，起灵，上路！", "next": "s5"}, "s5": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "（她终于穿上那身嫁衣的影子，就着灯火，端端正正拜了下去。一礼既成，身影随灯而起，淡如晨雾）替我向山下问好。就说——小夜先走一步，回有太阳的山坡去了。", "next": "s6"}, "s6": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（棺守的纸躯委顿于地，像卸下了肩上的棺。逢魔之刻的雾，第一次在天亮前散尽了。薄荷在哭，哭得很小声，怕吵到谁似的。）……结案。退魔寮乙字科凛音：逢魔神社夜巡，五夜，送行者一，安魂。", "next": ""}, "e_seal": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（立朱印）以逢魔之名，镇其归处。自此异象不起，百夜无更。", "next": "z1"}, "z1": {"speaker": "guanshou", "name": "棺守", "color": "ink_700", "portrait": "", "side": "right", "text": "镇……？你要……镇她？她等了七十年……你们山下人，七十年前弃她而去，如今还要把她钉在这口棺里——？！", "next": "z2"}, "z2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（朱印落下，钟鸣、纸响、棺纹一齐寂然。只有棺底极轻极轻地，叩了一声。像还有话，被封在了里面。）薄荷，记下来：本案未结，改「续监」。……我总有一天，会回来把这句话听完。", "next": "z3"}, "z3": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……没关系。已经，习惯了。", "next": ""}}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/config/stage_config.xlsx
+++ b/config/stage_config.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"t1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "五夜查明白了。水钵里的灯笼、无风的钟、夜行的棺、棺中的镜——都是同一件事：七十年前，一场没送成的葬。", "next": "t2"}, "t2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "钟鸣不是警报，是送行钟。纸人形列队不是在作乱，是在等一个替他们把仪式办完的人。第三次叩门，是它最后的耐心。", "next": "t3"}, "t3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "现在，轮到我了。", "next": "", "choices": [{"text": "（送行）念引路词，送它远行", "next": "e_send"}, {"text": "（镇守）立朱印，镇其归处", "next": "e_seal"}]}, "e_send": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……谢谢你。七十年了，终于有人听懂钟声里的意思。", "next": "s1"}, "s1": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "我叫小夜。山下村子，顾家的媳妇——虽然还没来得及过门。（她低头看自己的手）外头……仗打完了吗？", "next": "s2"}, "s2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "打完了。七十年前就打完了。村子的人迁去了南边，开枝散叶，活得很好。顾家的后人里，有一个做了退魔师——她让我替她还一盏灯。", "next": "s3"}, "s3": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "那就好，那就好……（她转向棺守的纸躯，端端正正福了一礼）祭主爷爷，更次你替我数了三万次，辛苦你了。", "next": "s4"}, "s4": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（引路词）魂兮归来，莫恋此乡。灯前有路，路尽有光。顾氏小夜——拜堂，起灵，上路！", "next": "s5"}, "s5": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "（她终于穿上那身嫁衣的影子，就着灯火，端端正正拜了下去。一礼既成，身影随灯而起，淡如晨雾）替我向山下问好。就说——小夜先走一步，回有太阳的山坡去了。", "next": "s6"}, "s6": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（棺守的纸躯委顿于地，像卸下了肩上的棺。逢魔之刻的雾，第一次在天亮前散尽了。薄荷在哭，哭得很小声，怕吵到谁似的。）……结案。退魔寮乙字科凛音：逢魔神社夜巡，五夜，送行者一，安魂。", "next": ""}, "e_seal": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（立朱印）以逢魔之名，镇其归处。自此异象不起，百夜无更。", "next": "z1"}, "z1": {"speaker": "guanshou", "name": "棺守", "color": "ink_700", "portrait": "", "side": "right", "text": "镇……？你要……镇她？她等了七十年……你们山下人，七十年前弃她而去，如今还要把她钉在这口棺里——？！", "next": "z2"}, "z2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（朱印落下，钟鸣、纸响、棺纹一齐寂然。只有棺底极轻极轻地，叩了一声。像还有话，被封在了里面。）薄荷，记下来：本案未结，改「续监」。……我总有一天，会回来把这句话听完。", "next": "z3"}, "z3": {"speaker": "sayo", "name": "？？？", "color": "paper_300", "portrait": "", "side": "right", "text": "……没关系。已经，习惯了。", "next": ""}}</t>
+          <t>{"t1": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "五夜查明白了。水钵里的灯笼、无风的钟、夜行的棺、棺中的镜——都是同一件事：七十年前，一场没送成的葬。", "next": "t2"}, "t2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "钟鸣不是警报，是送行钟。纸人形列队不是在作乱，是在等一个替他们把仪式办完的人。第三次叩门，是它最后的耐心。", "next": "t3"}, "t3": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "现在，轮到我了。", "next": "", "choices": [{"text": "（送行）念引路词，送它远行", "next": "e_send"}, {"text": "（镇守）立朱印，镇其归处", "next": "e_seal"}]}, "e_send": {"speaker": "sayo", "name": "小夜", "color": "paper_300", "portrait": "res://assets/chars/portraits/sayo_half.png", "side": "right", "text": "……谢谢你。七十年了，终于有人听懂钟声里的意思。", "next": "s1"}, "s1": {"speaker": "sayo", "name": "小夜", "color": "paper_300", "portrait": "res://assets/chars/portraits/sayo_half.png", "side": "right", "text": "我叫小夜。山下村子，顾家的媳妇——虽然还没来得及过门。（她低头看自己的手）外头……仗打完了吗？", "next": "s2"}, "s2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "打完了。七十年前就打完了。村子的人迁去了南边，开枝散叶，活得很好。顾家的后人里，有一个做了退魔师——她让我替她还一盏灯。", "next": "s3"}, "s3": {"speaker": "sayo", "name": "小夜", "color": "paper_300", "portrait": "res://assets/chars/portraits/sayo_half.png", "side": "right", "text": "那就好，那就好……（她转向棺守的纸躯，端端正正福了一礼）祭主爷爷，更次你替我数了三万次，辛苦你了。", "next": "s4"}, "s4": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（引路词）魂兮归来，莫恋此乡。灯前有路，路尽有光。顾氏小夜——拜堂，起灵，上路！", "next": "s5"}, "s5": {"speaker": "sayo", "name": "小夜", "color": "paper_300", "portrait": "res://assets/chars/portraits/sayo_half.png", "side": "right", "text": "（她终于穿上那身嫁衣的影子，就着灯火，端端正正拜了下去。一礼既成，身影随灯而起，淡如晨雾）替我向山下问好。就说——小夜先走一步，回有太阳的山坡去了。", "next": "s6"}, "s6": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（棺守的纸躯委顿于地，像卸下了肩上的棺。逢魔之刻的雾，第一次在天亮前散尽了。薄荷在哭，哭得很小声，怕吵到谁似的。）……结案。退魔寮乙字科凛音：逢魔神社夜巡，五夜，送行者一，安魂。", "next": ""}, "e_seal": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（立朱印）以逢魔之名，镇其归处。自此异象不起，百夜无更。", "next": "z1"}, "z1": {"speaker": "guanshou", "name": "棺守", "color": "ink_700", "portrait": "", "side": "right", "text": "镇……？你要……镇她？她等了七十年……你们山下人，七十年前弃她而去，如今还要把她钉在这口棺里——？！", "next": "z2"}, "z2": {"speaker": "rinne", "name": "凛音", "color": "vermilion_500", "portrait": "res://assets/chars/portraits/rinne_half.png", "side": "left", "text": "（朱印落下，钟鸣、纸响、棺纹一齐寂然。只有棺底极轻极轻地，叩了一声。像还有话，被封在了里面。）薄荷，记下来：本案未结，改「续监」。……我总有一天，会回来把这句话听完。", "next": "z3"}, "z3": {"speaker": "sayo", "name": "小夜", "color": "paper_300", "portrait": "res://assets/chars/portraits/sayo_half.png", "side": "right", "text": "……没关系。已经，习惯了。", "next": ""}}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
